--- a/business_surveys/022_sustainable_gift_ideas_survey--business_surveys.xlsx
+++ b/business_surveys/022_sustainable_gift_ideas_survey--business_surveys.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="survey" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="choices" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="settings" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="survey" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="choices" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="settings" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -437,13 +437,13 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E28"/>
+  <dimension ref="A1:E11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="17" customWidth="1" min="1" max="1"/>
-    <col width="21" customWidth="1" min="2" max="2"/>
-    <col width="44" customWidth="1" min="3" max="3"/>
-    <col width="6" customWidth="1" min="4" max="4"/>
+    <col width="20" customWidth="1" min="2" max="2"/>
+    <col width="46" customWidth="1" min="3" max="3"/>
+    <col width="50" customWidth="1" min="4" max="4"/>
     <col width="10" customWidth="1" min="5" max="5"/>
   </cols>
   <sheetData>
@@ -520,15 +520,19 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>intro</t>
+          <t>introduction</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>introduction</t>
-        </is>
-      </c>
-      <c r="D4" t="inlineStr"/>
+          <t>Welcome to the Sustainable Gift Ideas Survey</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>This survey will help us understand your gifting preferences.</t>
+        </is>
+      </c>
       <c r="E4" t="inlineStr">
         <is>
           <t>no</t>
@@ -551,7 +555,11 @@
           <t>What motivates you to give gifts?</t>
         </is>
       </c>
-      <c r="D5" t="inlineStr"/>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>Select all that apply.</t>
+        </is>
+      </c>
       <c r="E5" t="inlineStr">
         <is>
           <t>no</t>
@@ -566,15 +574,19 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>preference</t>
+          <t>gift_type</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>What are your gifting preferences?</t>
-        </is>
-      </c>
-      <c r="D6" t="inlineStr"/>
+          <t>What type of gift do you like to give?</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>Choose one that best describes your preference.</t>
+        </is>
+      </c>
       <c r="E6" t="inlineStr">
         <is>
           <t>no</t>
@@ -584,20 +596,24 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>select_multiple</t>
+          <t>select_one</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>idea</t>
+          <t>gift_frequency</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>What gift ideas do you like?</t>
-        </is>
-      </c>
-      <c r="D7" t="inlineStr"/>
+          <t>How often do you gift?</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>Select one that best describes your gifting frequency.</t>
+        </is>
+      </c>
       <c r="E7" t="inlineStr">
         <is>
           <t>no</t>
@@ -612,15 +628,19 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>frequency</t>
+          <t>budget</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>How often do you give gifts?</t>
-        </is>
-      </c>
-      <c r="D8" t="inlineStr"/>
+          <t>What is your budget for gifting?</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>Enter a number in dollars.</t>
+        </is>
+      </c>
       <c r="E8" t="inlineStr">
         <is>
           <t>no</t>
@@ -630,20 +650,24 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>text</t>
+          <t>select_one</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>budget</t>
+          <t>gifting_frequency2</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>What is your budget for gifting?</t>
-        </is>
-      </c>
-      <c r="D9" t="inlineStr"/>
+          <t>How often do you give this type of gift?</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>Select one that best describes your gifting frequency for this type of gift.</t>
+        </is>
+      </c>
       <c r="E9" t="inlineStr">
         <is>
           <t>no</t>
@@ -653,20 +677,24 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>select_one</t>
+          <t>text</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>gift_type</t>
+          <t>open_ended</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>What type of gift do you give?</t>
-        </is>
-      </c>
-      <c r="D10" t="inlineStr"/>
+          <t>Do you have any open-ended gift ideas?</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>Please describe your idea.</t>
+        </is>
+      </c>
       <c r="E10" t="inlineStr">
         <is>
           <t>no</t>
@@ -681,407 +709,20 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>gift_frequency</t>
+          <t>gifting_frequency3</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>How often do you give this type of gift?</t>
-        </is>
-      </c>
-      <c r="D11" t="inlineStr"/>
+          <t>Gifting Frequency3</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>Select one that best describes your gifting frequency for this type of gift.</t>
+        </is>
+      </c>
       <c r="E11" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" t="inlineStr">
-        <is>
-          <t>select_one</t>
-        </is>
-      </c>
-      <c r="B12" t="inlineStr">
-        <is>
-          <t>favorite</t>
-        </is>
-      </c>
-      <c r="C12" t="inlineStr">
-        <is>
-          <t>Which gift type do you like most?</t>
-        </is>
-      </c>
-      <c r="D12" t="inlineStr"/>
-      <c r="E12" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" t="inlineStr">
-        <is>
-          <t>text</t>
-        </is>
-      </c>
-      <c r="B13" t="inlineStr">
-        <is>
-          <t>open_ended</t>
-        </is>
-      </c>
-      <c r="C13" t="inlineStr">
-        <is>
-          <t>Do you have an open-ended gift idea?</t>
-        </is>
-      </c>
-      <c r="D13" t="inlineStr"/>
-      <c r="E13" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" t="inlineStr">
-        <is>
-          <t>select_multiple</t>
-        </is>
-      </c>
-      <c r="B14" t="inlineStr">
-        <is>
-          <t>motivation2</t>
-        </is>
-      </c>
-      <c r="C14" t="inlineStr">
-        <is>
-          <t>What motivates you to give gifts?</t>
-        </is>
-      </c>
-      <c r="D14" t="inlineStr"/>
-      <c r="E14" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" t="inlineStr">
-        <is>
-          <t>select_one</t>
-        </is>
-      </c>
-      <c r="B15" t="inlineStr">
-        <is>
-          <t>preference2</t>
-        </is>
-      </c>
-      <c r="C15" t="inlineStr">
-        <is>
-          <t>What are your gifting preferences 2?</t>
-        </is>
-      </c>
-      <c r="D15" t="inlineStr"/>
-      <c r="E15" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" t="inlineStr">
-        <is>
-          <t>text</t>
-        </is>
-      </c>
-      <c r="B16" t="inlineStr">
-        <is>
-          <t>budget2</t>
-        </is>
-      </c>
-      <c r="C16" t="inlineStr">
-        <is>
-          <t>What is your budget for gifting 2?</t>
-        </is>
-      </c>
-      <c r="D16" t="inlineStr"/>
-      <c r="E16" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" t="inlineStr">
-        <is>
-          <t>select_one</t>
-        </is>
-      </c>
-      <c r="B17" t="inlineStr">
-        <is>
-          <t>gift_type2</t>
-        </is>
-      </c>
-      <c r="C17" t="inlineStr">
-        <is>
-          <t>What type of gift do you give 2?</t>
-        </is>
-      </c>
-      <c r="D17" t="inlineStr"/>
-      <c r="E17" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" t="inlineStr">
-        <is>
-          <t>select_one</t>
-        </is>
-      </c>
-      <c r="B18" t="inlineStr">
-        <is>
-          <t>gift_frequency2</t>
-        </is>
-      </c>
-      <c r="C18" t="inlineStr">
-        <is>
-          <t>How often do you give this type of gift 2?</t>
-        </is>
-      </c>
-      <c r="D18" t="inlineStr"/>
-      <c r="E18" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" t="inlineStr">
-        <is>
-          <t>select_one</t>
-        </is>
-      </c>
-      <c r="B19" t="inlineStr">
-        <is>
-          <t>favorite2</t>
-        </is>
-      </c>
-      <c r="C19" t="inlineStr">
-        <is>
-          <t>Which gift type do you like most 2?</t>
-        </is>
-      </c>
-      <c r="D19" t="inlineStr"/>
-      <c r="E19" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="20">
-      <c r="A20" t="inlineStr">
-        <is>
-          <t>text</t>
-        </is>
-      </c>
-      <c r="B20" t="inlineStr">
-        <is>
-          <t>open_ended2</t>
-        </is>
-      </c>
-      <c r="C20" t="inlineStr">
-        <is>
-          <t>Do you have an open-ended gift idea 2?</t>
-        </is>
-      </c>
-      <c r="D20" t="inlineStr"/>
-      <c r="E20" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="21">
-      <c r="A21" t="inlineStr">
-        <is>
-          <t>select_multiple</t>
-        </is>
-      </c>
-      <c r="B21" t="inlineStr">
-        <is>
-          <t>motivation3</t>
-        </is>
-      </c>
-      <c r="C21" t="inlineStr">
-        <is>
-          <t>What motivates you to give gifts 3?</t>
-        </is>
-      </c>
-      <c r="D21" t="inlineStr"/>
-      <c r="E21" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="22">
-      <c r="A22" t="inlineStr">
-        <is>
-          <t>select_one</t>
-        </is>
-      </c>
-      <c r="B22" t="inlineStr">
-        <is>
-          <t>preference3</t>
-        </is>
-      </c>
-      <c r="C22" t="inlineStr">
-        <is>
-          <t>What are your gifting preferences 3?</t>
-        </is>
-      </c>
-      <c r="D22" t="inlineStr"/>
-      <c r="E22" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="23">
-      <c r="A23" t="inlineStr">
-        <is>
-          <t>select_one</t>
-        </is>
-      </c>
-      <c r="B23" t="inlineStr">
-        <is>
-          <t>gift_frequency3</t>
-        </is>
-      </c>
-      <c r="C23" t="inlineStr">
-        <is>
-          <t>How often do you give this type of gift 3?</t>
-        </is>
-      </c>
-      <c r="D23" t="inlineStr"/>
-      <c r="E23" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="24">
-      <c r="A24" t="inlineStr">
-        <is>
-          <t>select_one</t>
-        </is>
-      </c>
-      <c r="B24" t="inlineStr">
-        <is>
-          <t>gift_type3</t>
-        </is>
-      </c>
-      <c r="C24" t="inlineStr">
-        <is>
-          <t>What type of gift do you give 3?</t>
-        </is>
-      </c>
-      <c r="D24" t="inlineStr"/>
-      <c r="E24" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="25">
-      <c r="A25" t="inlineStr">
-        <is>
-          <t>select_one</t>
-        </is>
-      </c>
-      <c r="B25" t="inlineStr">
-        <is>
-          <t>favorite3</t>
-        </is>
-      </c>
-      <c r="C25" t="inlineStr">
-        <is>
-          <t>Which gift type do you like most 3?</t>
-        </is>
-      </c>
-      <c r="D25" t="inlineStr"/>
-      <c r="E25" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="26">
-      <c r="A26" t="inlineStr">
-        <is>
-          <t>select_multiple</t>
-        </is>
-      </c>
-      <c r="B26" t="inlineStr">
-        <is>
-          <t>motivation4</t>
-        </is>
-      </c>
-      <c r="C26" t="inlineStr">
-        <is>
-          <t>What motivates you to give gifts 4?</t>
-        </is>
-      </c>
-      <c r="D26" t="inlineStr"/>
-      <c r="E26" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="27">
-      <c r="A27" t="inlineStr">
-        <is>
-          <t>select_one</t>
-        </is>
-      </c>
-      <c r="B27" t="inlineStr">
-        <is>
-          <t>gifting_preferences</t>
-        </is>
-      </c>
-      <c r="C27" t="inlineStr">
-        <is>
-          <t>What are your gifting preferences?</t>
-        </is>
-      </c>
-      <c r="D27" t="inlineStr"/>
-      <c r="E27" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="28">
-      <c r="A28" t="inlineStr">
-        <is>
-          <t>text</t>
-        </is>
-      </c>
-      <c r="B28" t="inlineStr">
-        <is>
-          <t>gifting_frequency</t>
-        </is>
-      </c>
-      <c r="C28" t="inlineStr">
-        <is>
-          <t>How often do you give gifts?</t>
-        </is>
-      </c>
-      <c r="D28" t="inlineStr"/>
-      <c r="E28" t="inlineStr">
         <is>
           <t>no</t>
         </is>
@@ -1098,12 +739,12 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C51"/>
+  <dimension ref="A1:C28"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="29" customWidth="1" min="1" max="1"/>
-    <col width="9" customWidth="1" min="2" max="2"/>
-    <col width="9" customWidth="1" min="3" max="3"/>
+    <col width="28" customWidth="1" min="1" max="1"/>
+    <col width="32" customWidth="1" min="2" max="2"/>
+    <col width="32" customWidth="1" min="3" max="3"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -1131,12 +772,12 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>option1</t>
+          <t>to_show_love_and_appreciation</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>option1</t>
+          <t>To show love and appreciation</t>
         </is>
       </c>
     </row>
@@ -1148,12 +789,12 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>option2</t>
+          <t>to_celebrate_special_occasions</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>option2</t>
+          <t>To celebrate special occasions</t>
         </is>
       </c>
     </row>
@@ -1165,811 +806,420 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>option3</t>
+          <t>to_support_a_cause_or_charity</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>option3</t>
+          <t>To support a cause or charity</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>preference_choices</t>
+          <t>motivation_choices</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>option1</t>
+          <t>to_build_relationships</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>option1</t>
+          <t>To build relationships</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>preference_choices</t>
+          <t>motivation_choices</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>option2</t>
+          <t>other_(please_specify)</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>option2</t>
+          <t>Other (please specify)</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>preference_choices</t>
+          <t>gift_type_choices</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>option3</t>
+          <t>experience_gift</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>option3</t>
+          <t>Experience gift</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>preference_choices</t>
+          <t>gift_type_choices</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>option4</t>
+          <t>personalized_gift</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>option4</t>
+          <t>Personalized gift</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>idea_choices</t>
+          <t>gift_type_choices</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>option1</t>
+          <t>sustainable_gift</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>option1</t>
+          <t>Sustainable gift</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>idea_choices</t>
+          <t>gift_type_choices</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>option2</t>
+          <t>other_(please_specify)</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>option2</t>
+          <t>Other (please specify)</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>idea_choices</t>
+          <t>gift_frequency_choices</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>option3</t>
+          <t>daily</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>option3</t>
+          <t>Daily</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>idea_choices</t>
+          <t>gift_frequency_choices</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>option4</t>
+          <t>weekly</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>option4</t>
+          <t>Weekly</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>gift_type_choices</t>
+          <t>gift_frequency_choices</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>option1</t>
+          <t>monthly</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>option1</t>
+          <t>Monthly</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>gift_type_choices</t>
+          <t>gift_frequency_choices</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>option2</t>
+          <t>quarterly</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>option2</t>
+          <t>Quarterly</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>gift_type_choices</t>
+          <t>gift_frequency_choices</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>option3</t>
+          <t>yearly</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>option3</t>
+          <t>Yearly</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>gift_type_choices</t>
+          <t>gift_frequency_choices</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>option4</t>
+          <t>rarely</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>option4</t>
+          <t>Rarely</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>gift_frequency_choices</t>
+          <t>gifting_frequency2_choices</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>option1</t>
+          <t>daily</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>option1</t>
+          <t>Daily</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>gift_frequency_choices</t>
+          <t>gifting_frequency2_choices</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>option2</t>
+          <t>weekly</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>option2</t>
+          <t>Weekly</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>gift_frequency_choices</t>
+          <t>gifting_frequency2_choices</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>option3</t>
+          <t>monthly</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>option3</t>
+          <t>Monthly</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>favorite_choices</t>
+          <t>gifting_frequency2_choices</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>option1</t>
+          <t>quarterly</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>option1</t>
+          <t>Quarterly</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>favorite_choices</t>
+          <t>gifting_frequency2_choices</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>option2</t>
+          <t>yearly</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>option2</t>
+          <t>Yearly</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>motivation2_choices</t>
+          <t>gifting_frequency2_choices</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>option1</t>
+          <t>rarely</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>option1</t>
+          <t>Rarely</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>motivation2_choices</t>
+          <t>gifting_frequency3_choices</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>option2</t>
+          <t>daily</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>option2</t>
+          <t>Daily</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>motivation2_choices</t>
+          <t>gifting_frequency3_choices</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>option3</t>
+          <t>weekly</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>option3</t>
+          <t>Weekly</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>motivation2_choices</t>
+          <t>gifting_frequency3_choices</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>option4</t>
+          <t>monthly</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>option4</t>
+          <t>Monthly</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>preference2_choices</t>
+          <t>gifting_frequency3_choices</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>option1</t>
+          <t>quarterly</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>option1</t>
+          <t>Quarterly</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>preference2_choices</t>
+          <t>gifting_frequency3_choices</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>option2</t>
+          <t>yearly</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>option2</t>
+          <t>Yearly</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>preference2_choices</t>
+          <t>gifting_frequency3_choices</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>option3</t>
+          <t>rarely</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>option3</t>
-        </is>
-      </c>
-    </row>
-    <row r="29">
-      <c r="A29" t="inlineStr">
-        <is>
-          <t>gift_type2_choices</t>
-        </is>
-      </c>
-      <c r="B29" t="inlineStr">
-        <is>
-          <t>option1</t>
-        </is>
-      </c>
-      <c r="C29" t="inlineStr">
-        <is>
-          <t>option1</t>
-        </is>
-      </c>
-    </row>
-    <row r="30">
-      <c r="A30" t="inlineStr">
-        <is>
-          <t>gift_type2_choices</t>
-        </is>
-      </c>
-      <c r="B30" t="inlineStr">
-        <is>
-          <t>option2</t>
-        </is>
-      </c>
-      <c r="C30" t="inlineStr">
-        <is>
-          <t>option2</t>
-        </is>
-      </c>
-    </row>
-    <row r="31">
-      <c r="A31" t="inlineStr">
-        <is>
-          <t>gift_type2_choices</t>
-        </is>
-      </c>
-      <c r="B31" t="inlineStr">
-        <is>
-          <t>option3</t>
-        </is>
-      </c>
-      <c r="C31" t="inlineStr">
-        <is>
-          <t>option3</t>
-        </is>
-      </c>
-    </row>
-    <row r="32">
-      <c r="A32" t="inlineStr">
-        <is>
-          <t>gift_frequency2_choices</t>
-        </is>
-      </c>
-      <c r="B32" t="inlineStr">
-        <is>
-          <t>option1</t>
-        </is>
-      </c>
-      <c r="C32" t="inlineStr">
-        <is>
-          <t>option1</t>
-        </is>
-      </c>
-    </row>
-    <row r="33">
-      <c r="A33" t="inlineStr">
-        <is>
-          <t>gift_frequency2_choices</t>
-        </is>
-      </c>
-      <c r="B33" t="inlineStr">
-        <is>
-          <t>option2</t>
-        </is>
-      </c>
-      <c r="C33" t="inlineStr">
-        <is>
-          <t>option2</t>
-        </is>
-      </c>
-    </row>
-    <row r="34">
-      <c r="A34" t="inlineStr">
-        <is>
-          <t>favorite2_choices</t>
-        </is>
-      </c>
-      <c r="B34" t="inlineStr">
-        <is>
-          <t>option1</t>
-        </is>
-      </c>
-      <c r="C34" t="inlineStr">
-        <is>
-          <t>option1</t>
-        </is>
-      </c>
-    </row>
-    <row r="35">
-      <c r="A35" t="inlineStr">
-        <is>
-          <t>favorite2_choices</t>
-        </is>
-      </c>
-      <c r="B35" t="inlineStr">
-        <is>
-          <t>option2</t>
-        </is>
-      </c>
-      <c r="C35" t="inlineStr">
-        <is>
-          <t>option2</t>
-        </is>
-      </c>
-    </row>
-    <row r="36">
-      <c r="A36" t="inlineStr">
-        <is>
-          <t>motivation3_choices</t>
-        </is>
-      </c>
-      <c r="B36" t="inlineStr">
-        <is>
-          <t>option1</t>
-        </is>
-      </c>
-      <c r="C36" t="inlineStr">
-        <is>
-          <t>option1</t>
-        </is>
-      </c>
-    </row>
-    <row r="37">
-      <c r="A37" t="inlineStr">
-        <is>
-          <t>motivation3_choices</t>
-        </is>
-      </c>
-      <c r="B37" t="inlineStr">
-        <is>
-          <t>option2</t>
-        </is>
-      </c>
-      <c r="C37" t="inlineStr">
-        <is>
-          <t>option2</t>
-        </is>
-      </c>
-    </row>
-    <row r="38">
-      <c r="A38" t="inlineStr">
-        <is>
-          <t>motivation3_choices</t>
-        </is>
-      </c>
-      <c r="B38" t="inlineStr">
-        <is>
-          <t>option3</t>
-        </is>
-      </c>
-      <c r="C38" t="inlineStr">
-        <is>
-          <t>option3</t>
-        </is>
-      </c>
-    </row>
-    <row r="39">
-      <c r="A39" t="inlineStr">
-        <is>
-          <t>preference3_choices</t>
-        </is>
-      </c>
-      <c r="B39" t="inlineStr">
-        <is>
-          <t>option1</t>
-        </is>
-      </c>
-      <c r="C39" t="inlineStr">
-        <is>
-          <t>option1</t>
-        </is>
-      </c>
-    </row>
-    <row r="40">
-      <c r="A40" t="inlineStr">
-        <is>
-          <t>preference3_choices</t>
-        </is>
-      </c>
-      <c r="B40" t="inlineStr">
-        <is>
-          <t>option2</t>
-        </is>
-      </c>
-      <c r="C40" t="inlineStr">
-        <is>
-          <t>option2</t>
-        </is>
-      </c>
-    </row>
-    <row r="41">
-      <c r="A41" t="inlineStr">
-        <is>
-          <t>gift_frequency3_choices</t>
-        </is>
-      </c>
-      <c r="B41" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
-      <c r="C41" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-    </row>
-    <row r="42">
-      <c r="A42" t="inlineStr">
-        <is>
-          <t>gift_frequency3_choices</t>
-        </is>
-      </c>
-      <c r="B42" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-      <c r="C42" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-    </row>
-    <row r="43">
-      <c r="A43" t="inlineStr">
-        <is>
-          <t>gift_type3_choices</t>
-        </is>
-      </c>
-      <c r="B43" t="inlineStr">
-        <is>
-          <t>option1</t>
-        </is>
-      </c>
-      <c r="C43" t="inlineStr">
-        <is>
-          <t>option1</t>
-        </is>
-      </c>
-    </row>
-    <row r="44">
-      <c r="A44" t="inlineStr">
-        <is>
-          <t>gift_type3_choices</t>
-        </is>
-      </c>
-      <c r="B44" t="inlineStr">
-        <is>
-          <t>option2</t>
-        </is>
-      </c>
-      <c r="C44" t="inlineStr">
-        <is>
-          <t>option2</t>
-        </is>
-      </c>
-    </row>
-    <row r="45">
-      <c r="A45" t="inlineStr">
-        <is>
-          <t>favorite3_choices</t>
-        </is>
-      </c>
-      <c r="B45" t="inlineStr">
-        <is>
-          <t>option1</t>
-        </is>
-      </c>
-      <c r="C45" t="inlineStr">
-        <is>
-          <t>option1</t>
-        </is>
-      </c>
-    </row>
-    <row r="46">
-      <c r="A46" t="inlineStr">
-        <is>
-          <t>favorite3_choices</t>
-        </is>
-      </c>
-      <c r="B46" t="inlineStr">
-        <is>
-          <t>option2</t>
-        </is>
-      </c>
-      <c r="C46" t="inlineStr">
-        <is>
-          <t>option2</t>
-        </is>
-      </c>
-    </row>
-    <row r="47">
-      <c r="A47" t="inlineStr">
-        <is>
-          <t>motivation4_choices</t>
-        </is>
-      </c>
-      <c r="B47" t="inlineStr">
-        <is>
-          <t>option1</t>
-        </is>
-      </c>
-      <c r="C47" t="inlineStr">
-        <is>
-          <t>option1</t>
-        </is>
-      </c>
-    </row>
-    <row r="48">
-      <c r="A48" t="inlineStr">
-        <is>
-          <t>motivation4_choices</t>
-        </is>
-      </c>
-      <c r="B48" t="inlineStr">
-        <is>
-          <t>option2</t>
-        </is>
-      </c>
-      <c r="C48" t="inlineStr">
-        <is>
-          <t>option2</t>
-        </is>
-      </c>
-    </row>
-    <row r="49">
-      <c r="A49" t="inlineStr">
-        <is>
-          <t>gifting_preferences_choices</t>
-        </is>
-      </c>
-      <c r="B49" t="inlineStr">
-        <is>
-          <t>option1</t>
-        </is>
-      </c>
-      <c r="C49" t="inlineStr">
-        <is>
-          <t>option1</t>
-        </is>
-      </c>
-    </row>
-    <row r="50">
-      <c r="A50" t="inlineStr">
-        <is>
-          <t>gifting_preferences_choices</t>
-        </is>
-      </c>
-      <c r="B50" t="inlineStr">
-        <is>
-          <t>option2</t>
-        </is>
-      </c>
-      <c r="C50" t="inlineStr">
-        <is>
-          <t>option2</t>
-        </is>
-      </c>
-    </row>
-    <row r="51">
-      <c r="A51" t="inlineStr">
-        <is>
-          <t>gifting_preferences_choices</t>
-        </is>
-      </c>
-      <c r="B51" t="inlineStr">
-        <is>
-          <t>option3</t>
-        </is>
-      </c>
-      <c r="C51" t="inlineStr">
-        <is>
-          <t>option3</t>
+          <t>Rarely</t>
         </is>
       </c>
     </row>
